--- a/光伏配储项目/电价数据/2026/端州站.xlsx
+++ b/光伏配储项目/电价数据/2026/端州站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.51015</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.3804</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.88787</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.65387</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.66991</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.53122</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.50626</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45431</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.43913</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42306</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.41941</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.40874</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.39802</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.39975</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.38483</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40197</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.42302</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41246</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35444</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39141</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.3849</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.41686</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39206</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.42063</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41382</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42382</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41283</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44383</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.35776</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30004</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.33206</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.25253</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.29513</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.30322</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.30812</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.31795</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.12275</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.09975000000000001</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.11138</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.09829</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.12258</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.18185</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.29112</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.34586</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.27437</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.06031</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.09062000000000001</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.22433</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.10789</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.27026</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.26446</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.6745800000000001</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.48813</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.22682</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.19417</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.05816</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.42109</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.42247</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.6325</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.2755</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.76988</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.65197</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.19688</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.7842</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.9085</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.46248</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.5319700000000001</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.43288</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.47678</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.72999</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.62729</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.57311</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.41929</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.5750700000000001</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.46453</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>0.62173</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>0.81238</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>0.6583600000000001</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.6309</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>0.76855</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.02503</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.48766</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.67803</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.5658300000000001</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>0.7521599999999999</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.56613</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.5541699999999999</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.6437200000000001</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.61582</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.47402</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.47477</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.39954</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.416</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42566</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32918</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.6996100000000001</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.37745</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.7314700000000001</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.22107</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.7720399999999999</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.52438</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.51883</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50519</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.50915</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.48933</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.4016</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.46996</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.37997</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38004</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39124</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33686</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.37031</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35573</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.35887</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.37517</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.37511</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.35915</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.38004</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.41925</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.50003</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.59404</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.67638</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.36746</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.41546</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34765</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.33595</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.42289</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.51579</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.3694</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.29739</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.39952</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.05802</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.87121</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.8968700000000001</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.86811</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.84533</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.77504</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.6951799999999999</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.5920700000000001</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.7044199999999999</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>1.51147</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.33429</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.39077</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.40976</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.41967</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>1.16914</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>1.79244</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.5046</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.36847</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.13171</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.28405</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.83104</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.7934600000000001</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.33632</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.31979</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.49817</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.33943</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.36761</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>1.01299</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.85862</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.67162</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>0.69748</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>0.37847</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>0.4278</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>0.29419</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.41295</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>0.35968</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>0.58373</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>0.7107899999999999</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>0.5760700000000001</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>0.69472</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.7473099999999999</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.7265900000000001</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.57797</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.53044</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.73273</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.5372899999999999</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.8832300000000001</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.14424</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.7164700000000001</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.9313400000000001</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.84146</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.55912</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.5513899999999999</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.68113</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.74417</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.44545</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.40501</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33456</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32146</v>
+      </c>
+      <c r="C119" t="n">
+        <v>1.12396</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.42455</v>
+      </c>
+      <c r="E119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F119" t="n">
+        <v>1.75668</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.45286</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.48762</v>
+      </c>
+      <c r="I119" t="n">
+        <v>1.05942</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.39001</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.46663</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.42321</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.55136</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.58187</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.3716</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37073</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39614</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.43098</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.42845</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35579</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36128</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.3516</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36676</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.359</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.38463</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39646</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47385</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.57743</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.57112</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.39302</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.4817</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35298</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.42714</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.3898</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.34988</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.20851</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.26726</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.33962</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.33523</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.35389</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.35303</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.3429</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.47573</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.48809</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.52228</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.32727</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.48646</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.41553</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.29599</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.16245</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.31695</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.27281</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.31957</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.29972</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.28344</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.29372</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.33923</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.30034</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.2819700000000001</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.38937</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.39505</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.35306</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.41808</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.49538</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.34629</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.43024</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>0.41687</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.38116</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.39312</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.3445299999999999</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.36182</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.54273</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.6219199999999999</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.63879</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.92841</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.33155</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.47803</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.48559</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.50332</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.41408</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.4526</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.4438</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.46433</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.4505</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.40526</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.38079</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.42907</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.40764</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.40036</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.40442</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36611</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34912</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34239</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31923</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.39879</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.40313</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.32219</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.37551</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.37193</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.37074</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.34824</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.3409700000000001</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.36323</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.34383</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.33826</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.4576</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.34091</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.33199</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.33852</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.3413</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.34098</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.31639</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.31863</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.31597</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.31204</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.31602</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.33897</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33923</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35382</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.36734</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.38934</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.34279</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.35535</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.32676</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.36111</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.37653</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.38208</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.31317</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.5257500000000001</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.48113</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.24546</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.22428</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.48323</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.90404</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.85621</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>1.2081</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.32713</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.6381100000000001</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.85336</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>1.09245</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.8543200000000001</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.28398</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.08136</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.67259</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.8402999999999999</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.30896</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.47937</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.50514</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>1.42198</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.06620000000000001</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.37833</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.29794</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.26724</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.40037</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.36132</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.33026</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.24108</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.25433</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.22855</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.28985</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.14101</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.29417</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.29077</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.30765</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.33624</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.31964</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.33805</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.35851</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.34208</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.38516</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.42369</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.58331</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.46739</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.45902</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.38252</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.36366</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.3686</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.37949</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.45975</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.5060899999999999</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.56497</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.5097200000000001</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.41639</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.34985</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.33304</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.48173</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31994</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.311</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.29886</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.32111</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.44001</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.38233</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.36877</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.33891</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.30124</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.32086</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.37806</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.3106</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.30911</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.29707</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.30584</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.3107</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.29759</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.30226</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.29019</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.2902</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.29025</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.29807</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.29216</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.29515</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31235</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.30798</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31648</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.3245</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32436</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33271</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32615</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.27936</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.26053</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.33541</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.04575</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.32432</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.37949</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.04451</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.04768</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.18698</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.0482</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>-0.03357</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>-0.04689</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>-0.04589</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>-0.04144</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>-0.04022</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>-0.04034</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>-0.04094</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>-0.04079</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>-0.03921</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.04165</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>-0.04497</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>-0.04222</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.04106</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.04164</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.04248</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.04588</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>-0.04256</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>-0.04672</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.21879</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.0475</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.05379</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.0564</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>0.00342</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.07474</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.44971</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.3785</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.37304</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.29018</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.32228</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.29383</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31996</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32956</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31533</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33541</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33515</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33539</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.33406</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.38659</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.39212</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.38751</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.36602</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.34137</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.3878</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39992</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.38977</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46762</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.35467</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39651</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.40012</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.41719</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35504</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.3581</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.33885</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35971</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.351</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.36801</v>
+      </c>
+      <c r="C122" t="n">
+        <v>1.01433</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.40039</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.44668</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.42372</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.42379</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.35915</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.36602</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.33335</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.30932</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.32438</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.38176</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.35503</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.34757</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.34623</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.3351</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.31543</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.33023</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.33556</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.32266</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.30023</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.32271</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33539</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.33902</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.35022</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.35208</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.34279</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31613</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10253</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04356</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04689</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04546</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04609000000000001</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04609000000000001</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04609000000000001</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04545</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04379</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>-0.03618</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>-0.04282</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.10521</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>-0.00094</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.04033</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>-0.04925</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.04294</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04369</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04374</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.0456</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.04547</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04543999999999999</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04344</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.0431</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04533</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04318</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.04167</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.04497</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04512</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04523</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04342</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04405</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>-0.04152</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>-0.04345</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04451</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04994</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04968</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.04727000000000001</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04765</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.20009</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14298</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.29029</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30487</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.30017</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29527</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29317</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29375</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29271</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29715</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29107</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29526</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26908</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29412</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29834</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30875</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30413</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30232</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31467</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31871</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34789</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.34985</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34475</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.36672</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36521</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33572</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33062</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.3179</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31068</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.40485</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.35019</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32091</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30744</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31489</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.3016</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28139</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.291</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28827</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28114</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27141</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27119</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.28129</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17257</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.15882</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17114</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14788</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15961</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15878</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23644</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.21419</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22674</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26907</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28597</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.291</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31959</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.29101</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28114</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.28128</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28073</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27141</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28118</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32269</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31047</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30523</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.31658</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30964</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35925</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31626</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29559</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.38302</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.38014</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.42779</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.45437</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33183</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41783</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.4147</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.38916</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40198</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30009</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30101</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29937</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.30006</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15647</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29418</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31086</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31331</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31295</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32189</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34609</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30074</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33092</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38534</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5077</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79096</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6220599999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40006</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.498</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.78104</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92045</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.4946</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.91603</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.86809</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.29927</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35905</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.89288</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.6326000000000001</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.1924</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.87142</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.54615</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33626</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.03665</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.5361699999999999</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.7955099999999999</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.5306900000000001</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.77754</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.78115</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8773300000000001</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87624</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.4974</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.40284</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.40539</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.45482</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.2125</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.8790399999999999</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55114</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.6273099999999999</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.5397000000000001</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49929</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45652</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42493</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43814</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45023</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38958</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45279</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.42014</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.35261</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.40005</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36529</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.3865</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41486</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43388</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34394</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.39039</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.3507</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.34336</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.33704</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.34799</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.40432</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.35031</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.45085</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.35447</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.40035</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.40025</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.58689</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.42803</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.59614</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.6025499999999999</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.67241</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.47092</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.4187</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.58087</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.45198</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.88129</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.63493</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>1.18007</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.1619</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.86349</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.34669</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.44269</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.33043</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.33437</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.30634</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.90961</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>1.19264</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.2979</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.7723099999999999</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.32017</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.35734</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.33288</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.321</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.33688</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.33764</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31801</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.30632</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31918</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.31989</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.34405</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.31506</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.31517</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.32018</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.30499</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29911</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.31224</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.3138</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.31225</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.31548</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.31026</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.31545</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.32256</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.32371</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.32499</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.35461</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.34098</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.34036</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.33823</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.33062</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.33755</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.33553</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.41033</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.41297</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.45277</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.41533</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.39179</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.37525</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.35351</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32855</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.92591</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.36063</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.46774</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.36853</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.42339</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.48115</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.3833</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.4101</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.36707</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.37554</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.356</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.34888</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.38935</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.3307</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35933</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.34582</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32302</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.40042</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.5005299999999999</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.35726</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.3879</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34363</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.351</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.35542</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.37085</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.3581</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36321</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31662</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31371</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33276</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.3383</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.34648</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.35681</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.31497</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.31354</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.29077</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.31485</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.28994</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.35964</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.1653</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.3145</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.31187</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.38387</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.31225</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.32807</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.29729</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.26233</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.19917</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.27724</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.20005</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.31381</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.27815</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.3115</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.31633</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.39748</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.37144</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.31795</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.31544</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.32554</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.30802</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.31721</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.29444</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.31682</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.29015</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.3112799999999999</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.33127</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.29007</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.35169</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.25568</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.35015</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32212</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.30014</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.34363</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.27639</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.35418</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.32918</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.34081</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.31013</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.35048</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.32597</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.3859</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.34019</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.43727</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.35021</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.3243</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.42323</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.35166</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44881</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.32737</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.42066</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35905</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40196</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.4007</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.59749</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.35038</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.89055</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.52121</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.29462</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.7623799999999999</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.87461</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.7124400000000001</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.6299400000000001</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.47606</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.47369</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.5345700000000001</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.46317</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.46043</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.43387</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.43136</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.44398</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.5349700000000001</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.43136</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.4563</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.42977</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.45993</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.40482</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.44941</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.47584</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.41179</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.44382</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.4566</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.43136</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.43134</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.41663</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.44413</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.51034</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.42819</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.5321399999999999</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.38042</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.38145</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.297</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.42624</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.4289</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.3156</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.37362</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.31171</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>1.10715</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.31111</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.78067</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>1.13508</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.26086</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>1.69553</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>1.00911</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.98153</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>1.21258</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30686</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.26366</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.26049</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.313</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.29037</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.29385</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.45822</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.29613</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.32569</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.31635</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.33755</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.36209</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.32037</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.34597</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.34632</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.42228</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.41671</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.35683</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.36773</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.34212</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.33614</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.3735</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.35984</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.36317</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.37158</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.36284</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.34974</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.57827</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.48359</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.8627400000000001</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.49304</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.43756</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.37537</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.42272</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.386</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.36895</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.33381</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.34051</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.32895</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.3242</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.31849</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.43784</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.33906</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.34648</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.33953</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33624</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.32572</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.32898</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.32577</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.32448</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.32377</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.30956</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.32695</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.32555</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.31923</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.3153</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.32175</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.31994</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.3097</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.3273</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.31086</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.31954</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.32032</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.40592</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.3253</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.35507</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.41046</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.38285</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.35666</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.33983</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.36264</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.33571</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.33986</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.32059</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.29336</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.37214</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>1.10729</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>1.04229</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>1.0518</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.99864</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.80772</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.5118199999999999</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.52579</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.68144</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.51873</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.27009</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.49695</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.26989</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.48577</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.73437</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.44496</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.7565599999999999</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.91399</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.44156</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>1.10926</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.39706</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.5014999999999999</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>1.26755</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.49758</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.50993</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.9837400000000001</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.71168</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.72133</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.71477</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.73534</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.43286</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.83649</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.81647</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>1.40027</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.3582</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.39216</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.35323</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.41402</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.36952</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.39449</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.46743</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.40861</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.40384</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.41077</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.40578</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.46218</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.45744</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.45664</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.46244</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.46244</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.41341</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.39924</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.40591</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.39873</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.36115</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.36366</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34775</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.34897</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.33926</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.57677</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.40103</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.49681</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.44385</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.43455</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.37913</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.39693</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.39217</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.40757</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.39208</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.38063</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.39293</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.36911</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.40573</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.3811</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.39296</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.35743</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.35394</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.36153</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.35107</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.3456</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.35151</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.3456</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.35109</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.36363</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.38113</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.39294</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.36911</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.34557</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.3458</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.34575</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.33129</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.35138</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.35924</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.3771600000000001</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.2981</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.31618</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31562</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.31783</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.30313</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.28185</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.27605</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.26415</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.19843</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.30681</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.2482</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.2409</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.26816</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30855</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.29299</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31656</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.30014</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.29249</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.26801</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.30475</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.29206</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.27619</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.24023</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.31038</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.31776</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.2951</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.30351</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.28363</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.31779</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.34127</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.34326</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.34854</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.33323</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.33184</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.33559</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.34949</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.36053</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.35371</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.36713</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.38038</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.95392</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>1.08546</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.67664</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.24359</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.33112</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.38889</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.36089</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.35764</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.35785</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.42766</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.33958</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.34241</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.37208</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.3674</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.36193</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.38753</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.38774</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.39341</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.34992</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.36563</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.34008</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36162</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.3987</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.37243</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.38784</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.37592</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35443</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.34937</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.35785</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.3554</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.34171</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.35069</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.34834</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.35151</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.33893</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.35153</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.34221</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.34396</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.34498</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.33979</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.33957</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.33314</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.3305</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.33385</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.3323</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.3499</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.34433</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.36182</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.31308</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.33122</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.33923</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.32598</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.3224</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.33568</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.3331</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>1.16083</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.50983</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.37667</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.34111</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.40506</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.42855</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.33042</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.51075</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.30939</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.29978</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.37121</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.30639</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.29696</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.25035</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.75624</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.41115</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.22639</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.28674</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.29868</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.32439</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.30015</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.2825</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.30682</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.31911</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.31589</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.29897</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.32684</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.36131</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.36538</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.3435</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.57141</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.3541</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.35281</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.36319</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.37283</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.3226</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.39332</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.32474</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.33286</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.33817</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.34706</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.34341</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.46235</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.36804</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.70235</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.36973</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.3923</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.33395</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.32219</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.32301</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.50066</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.26005</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.38693</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.30678</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.31756</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.32952</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.3282</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.30351</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.30872</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.30401</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.28802</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32296</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.30502</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.9112899999999999</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.343</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.33072</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.32517</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.33034</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.32557</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.32558</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.31911</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.32382</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.3259</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32409</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.32712</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.3283</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.32689</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.32741</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.32406</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.33104</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.32617</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.32078</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.31987</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.32306</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.32645</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.33075</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.33533</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.33822</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.34074</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.34083</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.33192</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.34016</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.32124</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.32111</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.33507</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.35411</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.35418</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.33562</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.32545</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.32132</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.32194</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.32471</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.31753</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.3409</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.30057</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.33692</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.34436</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.3127</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.32524</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.28068</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.32561</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.31877</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.32177</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32863</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.33441</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.34609</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.30332</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.33602</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.32707</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.32044</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.31453</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.35058</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.31188</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.31142</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.32726</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.36656</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.34566</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.3459</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.33481</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.35009</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.35011</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.35012</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.36068</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.33286</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.33061</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.34838</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.38173</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.37125</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.36373</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.3712</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.36486</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.37749</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.36312</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.39809</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38774</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37373</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.41542</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.35591</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.36771</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.3595</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.3613</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.35046</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.35007</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.34115</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34962</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.33464</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.34377</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.34389</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.35153</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.3444</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.35087</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.35007</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.34286</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34277</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34015</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.35186</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.3408</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.34363</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.34287</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33711</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.33461</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.34007</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.33467</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.35938</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32441</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.33359</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.33461</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.34288</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.33222</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.3347</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.34507</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.33157</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.34286</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.34286</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33191</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.3419700000000001</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.32525</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.34413</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.35119</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.33781</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.34266</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.31481</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.33252</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.33676</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.33834</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.33349</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.32461</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.33402</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.32475</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.32469</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.3359</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32837</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.33334</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.32553</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.38694</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32252</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.32262</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.32056</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.31729</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.3222</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.33096</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.32924</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.3223</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.32336</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.3303</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.33068</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.33249</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.33864</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34794</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.36433</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.38817</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.36037</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35842</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.3593</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.37309</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.35366</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.36511</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34914</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.36453</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.36268</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36508</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.35085</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.38687</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.37933</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.3837</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.38461</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.42151</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.41838</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.36917</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.37988</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.65539</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.85712</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.43999</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.29743</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.47317</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.39246</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.34355</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.34381</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.3509</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.33465</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.33869</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.30871</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.40415</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.37521</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.37098</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.36213</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.35925</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.35895</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.36211</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.35003</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.36043</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.35907</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35295</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.36045</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.3529</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35211</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35937</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.36125</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.36159</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.33639</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.37252</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35877</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35764</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.36006</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.36006</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.36735</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36689</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.37967</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35947</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35647</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.3549</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35571</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.3533</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.34498</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.32962</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.32725</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.34048</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.33352</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.26461</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.14318</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.30324</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.28575</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.2845</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.19992</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.26025</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.28026</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.32754</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.28005</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.22131</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.27049</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.28619</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.27963</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.28997</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.29317</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.30569</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.34222</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.32338</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.14727</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.29267</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.29861</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.35534</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.32968</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.3501</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.33873</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.34854</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.35877</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.3281</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.30738</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.33009</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.35379</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.33667</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.36399</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.32198</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.36268</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.43719</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.3875</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.5446</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.8725599999999999</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.5736100000000001</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>1.09202</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.7361599999999999</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.68157</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.90012</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.95408</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.44634</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.47469</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.4095299999999999</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.37773</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.36404</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.4776</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.43057</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.40918</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.37713</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.3748</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36727</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.36012</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34378</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.49013</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.51001</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.46699</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.4727</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.42126</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.39294</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.40516</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.41224</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.41851</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.42681</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.40935</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.40092</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.41881</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.42304</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.40439</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.39814</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.43479</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.39822</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.42701</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.40106</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.40815</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.40812</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.42292</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.40175</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.47229</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.45927</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.5939099999999999</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.53154</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.47254</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.31881</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.43938</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.50919</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.37796</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.3902</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.49081</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.53047</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.49793</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.6342899999999999</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.42421</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.3014</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.33533</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.37797</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.51201</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.4466</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.43558</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.38148</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.28946</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.33616</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.33286</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.34612</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.34886</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.37246</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.64507</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.37089</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.34512</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.16907</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.2932</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.40076</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.41664</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.32725</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.34566</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.39533</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.34289</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.38292</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.37309</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.38094</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.35565</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.36076</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.35469</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.39594</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.33952</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.43131</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.45069</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.5168700000000001</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.45346</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.5426799999999999</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.4931</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.87125</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.90049</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.67208</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.7229099999999999</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.80876</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.5729500000000001</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.50122</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.7577</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.7043700000000001</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.61986</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.6449199999999999</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.43555</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.47586</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.46418</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.47783</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.45128</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.418</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.54471</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.42951</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.44156</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.4465</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.41838</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.41852</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.43813</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.40314</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.39935</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.44423</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.3981</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.40402</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.38714</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.38675</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.37845</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.37351</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.36006</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35686</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36583</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.37651</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.37118</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.36014</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.35639</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36583</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.3785</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.39021</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.3727200000000001</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.36186</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.35766</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35249</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.37273</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.40107</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.3787</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.38727</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.41224</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.3929</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38409</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35373</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.37359</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.34517</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.34087</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.35546</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.38662</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.23997</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.39636</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.34672</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.35064</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.36727</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.35109</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.40538</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.35722</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.48455</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.41385</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.46481</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.33544</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.31925</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.11481</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.18112</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.30065</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.29582</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32104</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.3535</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.35351</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.34885</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.35113</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.37438</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.38045</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.37574</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.43229</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.41661</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.36988</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.43036</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.41867</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.41444</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.38924</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.3788</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.38526</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.39075</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.40916</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.40821</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34568</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.36931</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37663</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.38738</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.36006</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.37268</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35506</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.39809</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.38038</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.37504</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.3567</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.39559</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.38069</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36571</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.32998</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.44523</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.36142</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.39606</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.39573</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.35752</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.37905</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.35043</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.3786</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.35753</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.35864</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.35536</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.35037</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.3592</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.34635</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.35123</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.34933</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.34011</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.33133</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.33994</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.34027</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.33533</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.34034</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.34534</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.33064</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.33035</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.33089</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.33094</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.31927</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.31036</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.31768</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.27616</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.32031</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.3151600000000001</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.30958</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.228</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.28816</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.23049</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.28999</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.25032</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.26056</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.14017</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.29442</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.29958</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.25239</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04333</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.2513</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.29594</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.16994</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.18295</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.28117</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.31029</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.31969</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.22905</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.25031</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.2652</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.23259</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.27564</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28451</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.2834100000000001</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.32784</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.32832</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.30789</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.35329</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.34919</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.35418</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.3606</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.35444</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.35801</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.33125</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.37497</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.36147</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.3445299999999999</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.31051</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.35785</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.35847</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.38183</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.35577</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.37065</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.37061</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.3717</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.34535</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.36524</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.38057</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.34115</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.3638</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.36883</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.36039</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.34831</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.34853</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.34833</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.34869</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.35042</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.32166</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.32532</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.33767</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.34127</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.34417</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.33857</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.32996</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.32363</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.31872</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.31798</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.30886</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.30892</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.31384</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.31059</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.30947</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.3107799999999999</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.31065</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.3117200000000001</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.30664</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.30664</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.30907</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.30608</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.30597</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.30664</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.3071</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.31032</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.31103</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.29078</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.27532</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.26187</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.17853</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.22248</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.23989</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.01823</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.0007</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>-0.02218</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04932</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.12064</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>-0.007480000000000001</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03931</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.04934</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.01427</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.03947</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.03648</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04786</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04737</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02421</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.026</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04937</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>0.12721</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.04934</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04936</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04916</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.00035</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.3034</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.0494</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.04914</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04936</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.02953</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04933</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04919</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.04123</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.18512</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.21348</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.24896</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.28004</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.276</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.2777</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.27652</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.28155</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.2977</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.31602</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.3048</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.30589</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.2918</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.3112</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.3155</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.32034</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.30694</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.31769</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.30278</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.31702</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.3096</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.33973</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.42412</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.33623</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.34716</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.32306</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.30917</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.30664</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.30151</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.30558</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.32794</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.18934</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.65551</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.46644</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.22244</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.37934</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.3266</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.32491</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.32064</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.32116</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.32752</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.30646</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.30251</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.27601</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.26946</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.2946</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.27764</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.25455</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.28425</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.26662</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.30629</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.2901</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.29989</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.27621</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.31946</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.30365</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.33554</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.37491</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.33061</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.29756</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.29728</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.25777</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.21884</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.70936</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.7153999999999999</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.7118300000000001</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.66024</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.20353</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.33208</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.12351</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.25524</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.21649</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.16856</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.17184</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.13733</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.23965</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.15686</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.32523</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.06369</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.04439</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.1019</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.14461</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.04278</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.20183</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.01977</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.16666</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.17369</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.18486</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.00207</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.14946</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.15778</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.1572</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.18967</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25682</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29433</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.27744</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.31773</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.33061</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.33089</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.32683</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.33738</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.33311</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.33745</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.33046</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.35677</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.36433</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.37498</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.34004</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.38673</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.38077</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.4279</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.37532</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.37444</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.36378</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>0.36199</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.35366</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.36983</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.35609</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.36566</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.3742799999999999</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.33506</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.33128</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.32862</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.32958</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.32921</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.33704</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.32362</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33011</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.35601</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.36482</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.33869</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.33811</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.33822</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.33192</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.33155</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.33163</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.33357</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.32953</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.3383</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.34323</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.33883</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.3282</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.33831</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.07994</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.33302</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.32351</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.31915</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.32707</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.32706</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.33374</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.3269</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.33729</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.33806</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.56687</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.50629</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.42313</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.40862</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.33772</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.32388</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.33277</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.41175</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.41888</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.42159</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.432</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.37097</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.42844</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.37004</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.36446</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.36585</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.44884</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.3306</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.31186</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.32784</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.3323</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.31207</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.1409</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.27704</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.27014</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30535</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.32884</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.3345</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.32286</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.34113</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.28921</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.31203</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.31146</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.29168</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.3127799999999999</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.31967</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.32389</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.32978</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.36337</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.3338</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.361</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.35236</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.35312</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.3547</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.35414</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.36117</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.33514</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.36024</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.33646</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.351</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.34012</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.36476</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.36898</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.32158</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.42784</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.35842</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.38831</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.35865</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.37856</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.36117</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.35135</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.36744</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.3434700000000001</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.31051</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.32678</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.32092</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.32603</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.3258</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.3771600000000001</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.33156</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.33151</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.29529</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.31667</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.32048</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.34074</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.3293</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.33306</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.34463</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.34511</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.32222</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.34561</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.34014</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.33621</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.32073</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.32057</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.33024</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.3464100000000001</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.33117</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.34015</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.34995</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.32323</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.36215</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.35518</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.36939</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35932</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.35955</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.36556</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.33036</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.35358</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.34522</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.52708</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.32731</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.50825</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.37345</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.47705</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.37722</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.36048</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.35797</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.36083</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.3098399999999999</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.35339</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.34607</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.43022</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.35886</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.31115</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.4808</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.38001</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.34089</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.26257</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.33944</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.34794</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.35108</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>1.32877</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.27799</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.28728</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.3395</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.85492</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>1.34724</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.84475</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.84317</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.8566699999999999</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>1.40749</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>1.4038</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>1.46279</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>1.46942</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>1.35742</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>1.56578</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>1.38134</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>1.36597</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>1.40018</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.85287</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.85562</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.84597</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.84734</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.85365</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.84788</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.8518</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.85002</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.8490700000000001</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.8547100000000001</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.8509099999999999</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>1.27703</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.84597</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.8909199999999999</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.8478300000000001</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.347</v>
+      </c>
+      <c r="C140" t="n">
+        <v>1.4807</v>
+      </c>
+      <c r="D140" t="n">
+        <v>1.58331</v>
+      </c>
+      <c r="E140" t="n">
+        <v>1.5833</v>
+      </c>
+      <c r="F140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G140" t="n">
+        <v>1.38055</v>
+      </c>
+      <c r="H140" t="n">
+        <v>1.35994</v>
+      </c>
+      <c r="I140" t="n">
+        <v>1.37513</v>
+      </c>
+      <c r="J140" t="n">
+        <v>1.37408</v>
+      </c>
+      <c r="K140" t="n">
+        <v>1.37843</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.84622</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.8460800000000001</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.3667</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.60014</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.60001</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.5999099999999999</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.84597</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.84597</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.8459800000000001</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.84597</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.84597</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.8460800000000001</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.84596</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.8461000000000001</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.8469500000000001</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.84756</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.84878</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.84781</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.8462499999999999</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.60012</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.60022</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.36555</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.35556</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.60433</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.39936</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.60634</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.38295</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.45928</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.40012</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.37363</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.31123</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.35835</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.32912</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.37053</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.27331</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.38348</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.41179</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.36457</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29419</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.31459</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.33318</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.33899</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.31819</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.32092</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.34077</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.35082</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.32125</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.34359</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.35816</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.35516</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.30872</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.35775</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.35707</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.39214</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.38404</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.39407</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.37219</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.39921</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.48825</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.4089</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.45234</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.43558</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.42999</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.48857</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.5501200000000001</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.5505800000000001</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.3949</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.45132</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.50729</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.48091</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.5102300000000001</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.4527</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.40101</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.50039</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.48809</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.31248</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.70056</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.5180900000000001</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.52777</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.38327</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.41684</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.38003</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.36564</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.37735</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.36021</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.36429</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.26568</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.36956</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.33511</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.36645</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.33806</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.33833</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.34422</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.32965</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.33664</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.34318</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.34017</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.33687</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.36077</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.33861</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.33901</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.34102</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.32093</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.32862</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.32401</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.32266</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.8454400000000001</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.8453099999999999</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.84524</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.84584</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.84616</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.84496</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.84638</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.8462499999999999</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.8465</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.31347</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.8467</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.84733</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.8469800000000001</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.85265</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.85798</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.8539800000000001</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.24427</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.8540599999999999</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.31825</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.85848</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.28106</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.17983</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.06901</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.39403</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.35959</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.8665700000000001</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.8647100000000001</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.21323</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.172</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.0056</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.31979</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.26325</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.16639</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.06177000000000001</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.05479</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.07393999999999999</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.17031</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.08159999999999999</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.0596</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.18088</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.15578</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.17609</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.28839</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.32209</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.30985</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.29689</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.38163</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.35419</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.36153</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.38277</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.35838</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.36812</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.26366</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.35439</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.36288</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.35326</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.31627</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.42552</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.42226</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.4367</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.38494</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.402</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.42122</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.38865</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.39835</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.41526</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.39462</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.37759</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.40818</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.37064</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.41175</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.37498</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.36903</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.35512</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.12215</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.35992</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.34074</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.78026</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.51025</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.51222</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.8570099999999999</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.5711799999999999</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.34522</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.38984</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.38603</v>
+      </c>
+      <c r="K142" t="n">
+        <v>1.38155</v>
+      </c>
+      <c r="L142" t="n">
+        <v>1.3565</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.84756</v>
+      </c>
+      <c r="N142" t="n">
+        <v>1.35132</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.84545</v>
+      </c>
+      <c r="P142" t="n">
+        <v>1.35666</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.84533</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.84689</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.84748</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.84697</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.35744</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.36404</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.8459099999999999</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.8459500000000001</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.84678</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.84535</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.8458600000000001</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.84796</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.84624</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>1.35583</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.85541</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.31283</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.32673</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.8473099999999999</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.85487</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.8585199999999999</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.8588</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.85791</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.27942</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.86034</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.28843</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.85115</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.84256</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.01333</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.84184</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.01079</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>1.03869</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.83751</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.0337</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>-0.00577</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>1.0187</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>1.0455</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>1.01722</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.8473099999999999</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.8400700000000001</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>1.16272</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>1.27794</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.8476</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>1.17107</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.27026</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.83838</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.43736</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.46031</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.43309</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.5245</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.4720299999999999</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.44135</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.35576</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.45093</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.48783</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.4504</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.42899</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.4302</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.4213</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.46535</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.46995</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.47972</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.52013</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.5486</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.49038</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.47532</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.47859</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.47793</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.48277</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.47371</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.86119</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.49089</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.45981</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.4719</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.5883700000000001</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.6652400000000001</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.36123</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.3643</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.35817</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.36356</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.36592</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.33621</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.54625</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.44355</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.4163</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.33239</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.36406</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.35846</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.36071</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.3511</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.44609</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.35003</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.39028</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.37592</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.35177</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.35037</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.35481</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.33287</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.34074</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.34756</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.33526</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.84587</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.84576</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.84558</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.8459800000000001</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.84597</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.8465499999999999</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.84585</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.8460599999999999</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.8460299999999999</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.31985</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.28872</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.84739</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.84681</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.14963</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.21725</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.24115</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.24549</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.11967</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.15872</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.02921</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>-0.01198</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04715</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.04719</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.04558</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.04606</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.04407</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.04134</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.08159999999999999</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.02832</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.84573</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.10042</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.18025</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.20737</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.12642</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.27349</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.24228</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.1297</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.08447</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.84748</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>1.15537</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.84646</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.84845</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.8463999999999999</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.85046</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.84677</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.84714</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.84861</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.84799</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.84805</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.84784</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.40083</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.44055</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.46119</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.50546</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.5374800000000001</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.5093299999999999</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.48032</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.53973</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.538</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.8537</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.8517</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.8556</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.54483</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.85833</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.5447000000000001</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.5439700000000001</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.5444199999999999</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.54995</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.8622300000000001</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.5407999999999999</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.50837</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.47745</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.47686</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.45491</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.43046</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.37557</v>
       </c>
     </row>
   </sheetData>
